--- a/PNG_Stratification.xlsx
+++ b/PNG_Stratification.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thawsu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3501835-1DB1-47E4-9551-FEC476CF8BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5941B00-A08F-4FEF-B246-CAE8CE7DA26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{A1084656-27F8-4118-87A0-BE85924678C5}"/>
   </bookViews>
@@ -62,24 +62,6 @@
     <t>district_code</t>
   </si>
   <si>
-    <t>Elimination_cutoffs</t>
-  </si>
-  <si>
-    <t>HMMimplementedareas</t>
-  </si>
-  <si>
-    <t>Pop_poor_access_Cat</t>
-  </si>
-  <si>
-    <t>mean_ITN_usage_cat</t>
-  </si>
-  <si>
-    <t>altitude_cat</t>
-  </si>
-  <si>
-    <t>areasb1600m</t>
-  </si>
-  <si>
     <t>Strata</t>
   </si>
   <si>
@@ -516,6 +498,24 @@
   </si>
   <si>
     <t>Population_percentage</t>
+  </si>
+  <si>
+    <t>Elimination_areas</t>
+  </si>
+  <si>
+    <t>HMM_implementedareas</t>
+  </si>
+  <si>
+    <t>Population_proportion_pooraccess</t>
+  </si>
+  <si>
+    <t>altitude_category</t>
+  </si>
+  <si>
+    <t>mean_ITN_usage_category</t>
+  </si>
+  <si>
+    <t>areas_below1600m</t>
   </si>
 </sst>
 </file>
@@ -577,7 +577,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -585,18 +585,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -605,7 +636,21 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -916,4818 +961,4825 @@
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
     <col min="2" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="26.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
     <col min="5" max="5" width="25.28515625" customWidth="1"/>
-    <col min="7" max="8" width="8.7109375" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" customWidth="1"/>
-    <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="14" width="16" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="28.28515625" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="10" width="28.5703125" customWidth="1"/>
+    <col min="11" max="11" width="21" customWidth="1"/>
+    <col min="12" max="12" width="22.5703125" customWidth="1"/>
+    <col min="13" max="13" width="24" customWidth="1"/>
+    <col min="14" max="14" width="19" customWidth="1"/>
+    <col min="15" max="15" width="16.42578125" customWidth="1"/>
+    <col min="16" max="16" width="24" customWidth="1"/>
+    <col min="17" max="17" width="19.7109375" customWidth="1"/>
+    <col min="18" max="18" width="17" customWidth="1"/>
+    <col min="19" max="19" width="23.5703125" customWidth="1"/>
+    <col min="21" max="21" width="17.85546875" customWidth="1"/>
     <col min="24" max="24" width="11.5703125" customWidth="1"/>
     <col min="25" max="25" width="12.5703125" customWidth="1"/>
+    <col min="27" max="27" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:27" s="1" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="N1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="O1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="P1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="Q1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="R1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="S1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="T1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="U1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="V1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="W1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="X1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="Y1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="Z1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="AA1" s="11" t="s">
         <v>19</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F2">
         <v>101</v>
       </c>
       <c r="H2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M2">
         <v>1.0037110656080095</v>
       </c>
-      <c r="N2" s="4" t="s">
-        <v>33</v>
+      <c r="N2" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="V2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F3">
         <v>102</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M3">
         <v>0.79500989897117058</v>
       </c>
-      <c r="N3" s="5" t="s">
-        <v>36</v>
+      <c r="N3" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="O3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="T3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F4">
         <v>103</v>
       </c>
       <c r="H4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M4">
         <v>0.74823270555199184</v>
       </c>
-      <c r="N4" s="6" t="s">
-        <v>38</v>
+      <c r="N4" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="O4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F5">
         <v>201</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K5" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M5">
         <v>1.5649184875943916</v>
       </c>
-      <c r="N5" s="4" t="s">
-        <v>33</v>
+      <c r="N5" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="V5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F6">
         <v>202</v>
       </c>
       <c r="H6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M6">
         <v>0.7437927058288718</v>
       </c>
-      <c r="N6" s="4" t="s">
-        <v>33</v>
+      <c r="N6" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="V6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D7">
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F7">
         <v>301</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M7">
         <v>0.80049406867603523</v>
       </c>
-      <c r="N7" s="6" t="s">
-        <v>38</v>
+      <c r="N7" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="O7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F8">
         <v>302</v>
       </c>
       <c r="H8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I8" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L8" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M8">
         <v>0.51991995405091795</v>
       </c>
-      <c r="N8" s="6" t="s">
-        <v>38</v>
+      <c r="N8" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="O8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="P8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F9">
         <v>303</v>
       </c>
       <c r="H9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L9" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M9">
         <v>1.7514958310216926</v>
       </c>
-      <c r="N9" s="4" t="s">
-        <v>33</v>
+      <c r="N9" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F10">
         <v>304</v>
       </c>
       <c r="H10" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K10" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L10" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M10">
         <v>0.81403515137602034</v>
       </c>
-      <c r="N10" s="6" t="s">
-        <v>38</v>
+      <c r="N10" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="O10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D11">
         <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F11">
         <v>402</v>
       </c>
-      <c r="I11" s="9"/>
       <c r="J11" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K11" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L11" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M11">
         <v>5.1107469483266055</v>
       </c>
-      <c r="N11" s="6" t="s">
-        <v>38</v>
+      <c r="N11" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="O11" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q11" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U11" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z11" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D12">
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F12">
         <v>501</v>
       </c>
       <c r="H12" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K12" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L12" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M12">
         <v>1.2591008804087727</v>
       </c>
-      <c r="N12" s="5" t="s">
-        <v>36</v>
+      <c r="N12" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="O12" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q12" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S12" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="T12" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U12" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X12" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z12" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AA12" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D13">
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F13">
         <v>502</v>
       </c>
       <c r="H13" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I13" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J13" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K13" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L13" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M13">
         <v>0.741123786487206</v>
       </c>
-      <c r="N13" s="5" t="s">
-        <v>36</v>
+      <c r="N13" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="O13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="T13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="V13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AA13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F14">
         <v>503</v>
       </c>
       <c r="H14" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J14" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K14" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L14" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M14">
         <v>0.80849407641434123</v>
       </c>
-      <c r="N14" s="4" t="s">
-        <v>33</v>
+      <c r="N14" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O14" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q14" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S14" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U14" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X14" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z14" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D15">
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F15">
         <v>504</v>
       </c>
       <c r="H15" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I15" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J15" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K15" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L15" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M15">
         <v>0.6889706311418099</v>
       </c>
-      <c r="N15" s="5" t="s">
-        <v>36</v>
+      <c r="N15" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="O15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="T15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="V15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AA15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D16">
         <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F16">
         <v>601</v>
       </c>
       <c r="H16" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K16" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L16" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M16">
         <v>1.3642921209093262</v>
       </c>
-      <c r="N16" s="4" t="s">
-        <v>33</v>
+      <c r="N16" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O16" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q16" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U16" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X16" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z16" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F17">
         <v>602</v>
       </c>
       <c r="H17" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K17" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L17" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M17">
         <v>1.1835708003883192</v>
       </c>
-      <c r="N17" s="4" t="s">
-        <v>33</v>
+      <c r="N17" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O17" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q17" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U17" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X17" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z17" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D18">
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F18">
         <v>701</v>
       </c>
       <c r="G18" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="J18" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K18" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L18" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M18">
         <v>0.87945027102369489</v>
       </c>
-      <c r="N18" s="7" t="s">
-        <v>65</v>
+      <c r="N18" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="O18" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="P18" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R18" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U18" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W18" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y18" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z18" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19">
         <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F19">
         <v>702</v>
       </c>
       <c r="G19" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="J19" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K19" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="M19">
         <v>1.1221241257017103</v>
       </c>
-      <c r="N19" s="7" t="s">
-        <v>65</v>
+      <c r="N19" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="P19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D20">
         <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F20">
         <v>703</v>
       </c>
       <c r="G20" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="J20" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K20" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L20" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M20">
         <v>1.0271521415833156</v>
       </c>
-      <c r="N20" s="7" t="s">
-        <v>65</v>
+      <c r="N20" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="O20" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="P20" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R20" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U20" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W20" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y20" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z20" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D21">
         <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F21">
         <v>706</v>
       </c>
       <c r="G21" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="J21" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K21" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="M21">
         <v>2.0037495391771314</v>
       </c>
-      <c r="N21" s="7" t="s">
-        <v>65</v>
+      <c r="N21" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="R21" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U21" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W21" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y21" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z21" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D22">
         <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F22">
         <v>707</v>
       </c>
       <c r="G22" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="J22" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K22" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L22" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M22">
         <v>2.0366676185739672</v>
       </c>
-      <c r="N22" s="7" t="s">
-        <v>65</v>
+      <c r="N22" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="O22" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R22" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U22" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W22" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y22" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z22" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D23">
         <v>8</v>
       </c>
       <c r="E23" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F23">
         <v>801</v>
       </c>
       <c r="G23" t="s">
+        <v>58</v>
+      </c>
+      <c r="J23" t="s">
+        <v>46</v>
+      </c>
+      <c r="K23" t="s">
         <v>64</v>
-      </c>
-      <c r="J23" t="s">
-        <v>52</v>
-      </c>
-      <c r="K23" t="s">
-        <v>70</v>
       </c>
       <c r="M23">
         <v>1.0530640718450126</v>
       </c>
-      <c r="N23" s="7" t="s">
-        <v>65</v>
+      <c r="N23" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="R23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D24">
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F24">
         <v>802</v>
       </c>
       <c r="I24" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J24" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K24" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="L24" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M24">
         <v>0.78688095894041188</v>
       </c>
-      <c r="N24" s="6" t="s">
-        <v>38</v>
+      <c r="N24" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="O24" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="Q24" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U24" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z24" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D25">
         <v>8</v>
       </c>
       <c r="E25" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F25">
         <v>803</v>
       </c>
       <c r="G25" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="J25" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K25" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="M25">
         <v>2.2886302465901442</v>
       </c>
-      <c r="N25" s="8" t="s">
-        <v>77</v>
+      <c r="N25" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="R25" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U25" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W25" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y25" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z25" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D26">
         <v>8</v>
       </c>
       <c r="E26" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F26">
         <v>804</v>
       </c>
       <c r="G26" t="s">
+        <v>58</v>
+      </c>
+      <c r="J26" t="s">
+        <v>46</v>
+      </c>
+      <c r="K26" t="s">
         <v>64</v>
-      </c>
-      <c r="J26" t="s">
-        <v>52</v>
-      </c>
-      <c r="K26" t="s">
-        <v>70</v>
       </c>
       <c r="M26">
         <v>1.0609438295438338</v>
       </c>
-      <c r="N26" s="7" t="s">
-        <v>65</v>
+      <c r="N26" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="R26" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U26" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W26" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y26" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z26" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D27">
         <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F27">
         <v>805</v>
       </c>
       <c r="G27" t="s">
+        <v>58</v>
+      </c>
+      <c r="J27" t="s">
+        <v>46</v>
+      </c>
+      <c r="K27" t="s">
         <v>64</v>
-      </c>
-      <c r="J27" t="s">
-        <v>52</v>
-      </c>
-      <c r="K27" t="s">
-        <v>70</v>
       </c>
       <c r="M27">
         <v>1.0342650155434381</v>
       </c>
-      <c r="N27" s="7" t="s">
-        <v>65</v>
+      <c r="N27" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="R27" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U27" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W27" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y27" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z27" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D28">
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F28">
         <v>902</v>
       </c>
       <c r="J28" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K28" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="M28">
         <v>1.1224289227331619</v>
       </c>
-      <c r="N28" s="6" t="s">
-        <v>38</v>
+      <c r="N28" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P28" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q28" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U28" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z28" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D29">
         <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F29">
         <v>903</v>
       </c>
       <c r="G29" t="s">
-        <v>64</v>
-      </c>
-      <c r="I29" s="9"/>
+        <v>58</v>
+      </c>
       <c r="J29" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K29" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="M29">
         <v>1.7082349627737259</v>
       </c>
-      <c r="N29" s="7" t="s">
-        <v>65</v>
+      <c r="N29" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="P29" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R29" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U29" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W29" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y29" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z29" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D30">
         <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F30">
         <v>905</v>
       </c>
       <c r="J30" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K30" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L30" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M30">
         <v>1.1504148319846803</v>
       </c>
-      <c r="N30" s="6" t="s">
-        <v>38</v>
+      <c r="N30" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="O30" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="P30" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q30" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U30" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z30" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D31">
         <v>9</v>
       </c>
       <c r="E31" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F31">
         <v>907</v>
       </c>
       <c r="G31" t="s">
+        <v>58</v>
+      </c>
+      <c r="J31" t="s">
+        <v>46</v>
+      </c>
+      <c r="K31" t="s">
         <v>64</v>
       </c>
-      <c r="J31" t="s">
-        <v>52</v>
-      </c>
-      <c r="K31" t="s">
-        <v>70</v>
-      </c>
       <c r="L31" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M31">
         <v>1.0459941398912687</v>
       </c>
-      <c r="N31" s="7" t="s">
-        <v>65</v>
+      <c r="N31" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="O31" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="R31" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U31" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W31" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y31" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z31" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D32">
         <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F32">
         <v>1001</v>
       </c>
       <c r="G32" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="J32" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K32" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="M32">
         <v>0.55485321085952544</v>
       </c>
-      <c r="N32" s="8" t="s">
-        <v>77</v>
+      <c r="N32" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="P32" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R32" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U32" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W32" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y32" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z32" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D33">
         <v>10</v>
       </c>
       <c r="E33" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F33">
         <v>1002</v>
       </c>
       <c r="G33" t="s">
+        <v>58</v>
+      </c>
+      <c r="J33" t="s">
+        <v>46</v>
+      </c>
+      <c r="K33" t="s">
         <v>64</v>
-      </c>
-      <c r="J33" t="s">
-        <v>52</v>
-      </c>
-      <c r="K33" t="s">
-        <v>70</v>
       </c>
       <c r="M33">
         <v>0.80851217471291392</v>
       </c>
-      <c r="N33" s="7" t="s">
-        <v>65</v>
+      <c r="N33" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="R33" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U33" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W33" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y33" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z33" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B34">
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D34">
         <v>10</v>
       </c>
       <c r="E34" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F34">
         <v>1003</v>
       </c>
       <c r="G34" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="I34" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J34" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K34" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L34" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M34">
         <v>0.74166701584331485</v>
       </c>
-      <c r="N34" s="8" t="s">
-        <v>77</v>
+      <c r="N34" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="O34" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R34" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U34" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W34" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y34" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z34" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D35">
         <v>10</v>
       </c>
       <c r="E35" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F35">
         <v>1004</v>
       </c>
       <c r="G35" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="J35" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K35" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="M35">
         <v>1.323920911906354</v>
       </c>
-      <c r="N35" s="8" t="s">
-        <v>77</v>
+      <c r="N35" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="P35" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R35" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U35" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W35" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y35" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z35" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D36">
         <v>10</v>
       </c>
       <c r="E36" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F36">
         <v>1005</v>
       </c>
       <c r="G36" t="s">
+        <v>58</v>
+      </c>
+      <c r="J36" t="s">
+        <v>46</v>
+      </c>
+      <c r="K36" t="s">
         <v>64</v>
       </c>
-      <c r="J36" t="s">
-        <v>52</v>
-      </c>
-      <c r="K36" t="s">
-        <v>70</v>
-      </c>
       <c r="L36" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M36">
         <v>1.1165174898106354</v>
       </c>
-      <c r="N36" s="7" t="s">
-        <v>65</v>
+      <c r="N36" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="O36" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="R36" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U36" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W36" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y36" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z36" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B37">
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D37">
         <v>10</v>
       </c>
       <c r="E37" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F37">
         <v>1006</v>
       </c>
       <c r="G37" t="s">
+        <v>58</v>
+      </c>
+      <c r="J37" t="s">
+        <v>46</v>
+      </c>
+      <c r="K37" t="s">
         <v>64</v>
-      </c>
-      <c r="J37" t="s">
-        <v>52</v>
-      </c>
-      <c r="K37" t="s">
-        <v>70</v>
       </c>
       <c r="M37">
         <v>0.8077301105270327</v>
       </c>
-      <c r="N37" s="7" t="s">
-        <v>65</v>
+      <c r="N37" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="R37" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U37" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W37" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y37" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z37" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D38">
         <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F38">
         <v>1101</v>
       </c>
       <c r="G38" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="J38" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K38" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="M38">
         <v>0.5867016769797101</v>
       </c>
-      <c r="N38" s="8" t="s">
-        <v>77</v>
+      <c r="N38" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="P38" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R38" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U38" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W38" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y38" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z38" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B39">
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D39">
         <v>11</v>
       </c>
       <c r="E39" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F39">
         <v>1102</v>
       </c>
       <c r="G39" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="J39" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K39" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L39" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M39">
         <v>1.3250028742763496</v>
       </c>
-      <c r="N39" s="7" t="s">
-        <v>65</v>
+      <c r="N39" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="O39" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="P39" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R39" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U39" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W39" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y39" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z39" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B40">
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D40">
         <v>11</v>
       </c>
       <c r="E40" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F40">
         <v>1103</v>
       </c>
       <c r="G40" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="J40" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K40" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L40" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M40">
         <v>0.8061044992405848</v>
       </c>
-      <c r="N40" s="7" t="s">
-        <v>65</v>
+      <c r="N40" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="O40" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="P40" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R40" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U40" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W40" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y40" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z40" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B41">
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D41">
         <v>11</v>
       </c>
       <c r="E41" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F41">
         <v>1104</v>
       </c>
       <c r="J41" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K41" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L41" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M41">
         <v>1.6178475267093564</v>
       </c>
-      <c r="N41" s="6" t="s">
-        <v>38</v>
+      <c r="N41" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="O41" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="P41" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q41" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U41" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z41" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B42">
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D42">
         <v>11</v>
       </c>
       <c r="E42" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F42">
         <v>1105</v>
       </c>
       <c r="G42" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="J42" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K42" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L42" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M42">
         <v>0.78243549551908276</v>
       </c>
-      <c r="N42" s="7" t="s">
-        <v>65</v>
+      <c r="N42" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="O42" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="P42" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R42" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U42" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W42" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y42" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z42" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B43">
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D43">
         <v>11</v>
       </c>
       <c r="E43" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F43">
         <v>1106</v>
       </c>
       <c r="I43" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J43" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K43" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L43" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M43">
         <v>0.51155547350224007</v>
       </c>
-      <c r="N43" s="6" t="s">
-        <v>38</v>
+      <c r="N43" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="O43" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="P43" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q43" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U43" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z43" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B44">
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D44">
         <v>11</v>
       </c>
       <c r="E44" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="F44">
         <v>1107</v>
       </c>
       <c r="G44" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="J44" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K44" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="M44">
         <v>0.94051932329842702</v>
       </c>
-      <c r="N44" s="7" t="s">
-        <v>65</v>
+      <c r="N44" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="P44" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R44" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U44" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W44" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y44" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z44" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B45">
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D45">
         <v>11</v>
       </c>
       <c r="E45" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F45">
         <v>1108</v>
       </c>
       <c r="G45" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="J45" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K45" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L45" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M45">
         <v>0.8601959257205305</v>
       </c>
-      <c r="N45" s="7" t="s">
-        <v>65</v>
+      <c r="N45" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="O45" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="P45" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R45" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U45" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W45" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y45" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z45" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B46">
         <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D46">
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F46">
         <v>1201</v>
       </c>
       <c r="H46" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J46" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K46" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L46" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M46">
         <v>1.2039127494161617</v>
       </c>
-      <c r="N46" s="6" t="s">
-        <v>38</v>
+      <c r="N46" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="O46" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q46" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U46" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z46" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B47">
         <v>3</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D47">
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="F47">
         <v>1202</v>
       </c>
       <c r="H47" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I47" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J47" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K47" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L47" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M47">
         <v>0.64804188165643117</v>
       </c>
-      <c r="N47" s="4" t="s">
-        <v>33</v>
+      <c r="N47" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O47" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q47" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S47" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U47" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="V47" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X47" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z47" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D48">
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F48">
         <v>1203</v>
       </c>
       <c r="H48" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J48" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K48" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L48" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M48">
         <v>0.91938689839039023</v>
       </c>
-      <c r="N48" s="4" t="s">
-        <v>33</v>
+      <c r="N48" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O48" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q48" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S48" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U48" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X48" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z48" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B49">
         <v>3</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D49">
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F49">
         <v>1204</v>
       </c>
       <c r="H49" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I49" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J49" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K49" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L49" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M49">
         <v>0.51528527727846751</v>
       </c>
-      <c r="N49" s="6" t="s">
-        <v>38</v>
+      <c r="N49" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="O49" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="P49" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q49" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U49" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z49" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B50">
         <v>3</v>
       </c>
       <c r="C50" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D50">
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F50">
         <v>1205</v>
       </c>
       <c r="H50" t="s">
-        <v>29</v>
-      </c>
-      <c r="I50" s="9"/>
+        <v>23</v>
+      </c>
       <c r="J50" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K50" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L50" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M50">
         <v>1.7653546532524684</v>
       </c>
-      <c r="N50" s="5" t="s">
-        <v>36</v>
+      <c r="N50" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="O50" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q50" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S50" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="T50" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U50" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X50" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z50" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AA50" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B51">
         <v>3</v>
       </c>
       <c r="C51" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D51">
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F51">
         <v>1206</v>
       </c>
       <c r="H51" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J51" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K51" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L51" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M51">
         <v>0.74076999916078912</v>
       </c>
-      <c r="N51" s="4" t="s">
-        <v>33</v>
+      <c r="N51" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O51" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q51" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S51" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U51" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X51" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z51" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B52">
         <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D52">
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="F52">
         <v>1207</v>
       </c>
       <c r="H52" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I52" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J52" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K52" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L52" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M52">
         <v>1.0337116706426637</v>
       </c>
-      <c r="N52" s="6" t="s">
-        <v>38</v>
+      <c r="N52" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="O52" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="P52" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q52" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U52" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z52" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B53">
         <v>3</v>
       </c>
       <c r="C53" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D53">
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="F53">
         <v>1208</v>
       </c>
       <c r="H53" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I53" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J53" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K53" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L53" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M53">
         <v>0.52813422005933475</v>
       </c>
-      <c r="N53" s="4" t="s">
-        <v>33</v>
+      <c r="N53" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O53" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q53" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S53" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U53" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="V53" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X53" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z53" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B54">
         <v>3</v>
       </c>
       <c r="C54" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D54">
         <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="F54">
         <v>1209</v>
       </c>
       <c r="H54" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I54" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J54" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K54" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L54" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M54">
         <v>0.64410659659808434</v>
       </c>
-      <c r="N54" s="4" t="s">
-        <v>33</v>
+      <c r="N54" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O54" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q54" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S54" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U54" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="V54" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X54" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z54" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B55">
         <v>3</v>
       </c>
       <c r="C55" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D55">
         <v>13</v>
       </c>
       <c r="E55" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="F55">
         <v>1301</v>
       </c>
       <c r="H55" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K55" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L55" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M55">
         <v>0.97455862789196757</v>
       </c>
-      <c r="N55" s="5" t="s">
-        <v>36</v>
+      <c r="N55" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="O55" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q55" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="T55" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U55" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X55" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z55" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B56">
         <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D56">
         <v>13</v>
       </c>
       <c r="E56" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="F56">
         <v>1302</v>
       </c>
       <c r="H56" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K56" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L56" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M56">
         <v>1.4407738074812466</v>
       </c>
-      <c r="N56" s="5" t="s">
-        <v>36</v>
+      <c r="N56" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="O56" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q56" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="T56" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U56" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X56" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z56" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B57">
         <v>3</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D57">
         <v>13</v>
       </c>
       <c r="E57" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="F57">
         <v>1303</v>
       </c>
       <c r="H57" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I57" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K57" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L57" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M57">
         <v>1.0242167566527647</v>
       </c>
-      <c r="N57" s="4" t="s">
-        <v>33</v>
+      <c r="N57" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O57" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q57" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U57" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="V57" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X57" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z57" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B58">
         <v>3</v>
       </c>
       <c r="C58" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D58">
         <v>13</v>
       </c>
       <c r="E58" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="F58">
         <v>1304</v>
       </c>
       <c r="H58" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I58" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K58" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L58" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M58">
         <v>1.0803791265924276</v>
       </c>
-      <c r="N58" s="4" t="s">
-        <v>33</v>
+      <c r="N58" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O58" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q58" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U58" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="V58" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X58" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z58" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B59">
         <v>3</v>
       </c>
       <c r="C59" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D59">
         <v>13</v>
       </c>
       <c r="E59" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F59">
         <v>1305</v>
       </c>
       <c r="H59" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K59" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L59" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M59">
         <v>1.1027869514920705</v>
       </c>
-      <c r="N59" s="4" t="s">
-        <v>33</v>
+      <c r="N59" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O59" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q59" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U59" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X59" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z59" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B60">
         <v>3</v>
       </c>
       <c r="C60" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D60">
         <v>13</v>
       </c>
       <c r="E60" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="F60">
         <v>1306</v>
       </c>
       <c r="H60" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K60" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L60" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M60">
         <v>0.78942793086478558</v>
       </c>
-      <c r="N60" s="5" t="s">
-        <v>36</v>
+      <c r="N60" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="O60" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q60" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="T60" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U60" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X60" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z60" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B61">
         <v>3</v>
       </c>
       <c r="C61" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D61">
         <v>14</v>
       </c>
       <c r="E61" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="F61">
         <v>1401</v>
       </c>
       <c r="H61" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I61" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K61" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L61" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M61">
         <v>0.90431269192279962</v>
       </c>
-      <c r="N61" s="5" t="s">
-        <v>36</v>
+      <c r="N61" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="O61" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q61" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="T61" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U61" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="V61" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X61" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z61" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B62">
         <v>3</v>
       </c>
       <c r="C62" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D62">
         <v>14</v>
       </c>
       <c r="E62" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F62">
         <v>1402</v>
       </c>
       <c r="H62" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I62" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K62" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L62" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M62">
         <v>1.2413412320689876</v>
       </c>
-      <c r="N62" s="4" t="s">
-        <v>33</v>
+      <c r="N62" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O62" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q62" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U62" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="V62" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X62" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z62" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B63">
         <v>3</v>
       </c>
       <c r="C63" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D63">
         <v>14</v>
       </c>
       <c r="E63" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F63">
         <v>1403</v>
       </c>
       <c r="H63" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K63" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L63" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M63">
         <v>0.91372378762422446</v>
       </c>
-      <c r="N63" s="4" t="s">
-        <v>33</v>
+      <c r="N63" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O63" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q63" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U63" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X63" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z63" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B64">
         <v>3</v>
       </c>
       <c r="C64" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D64">
         <v>14</v>
       </c>
       <c r="E64" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="F64">
         <v>1404</v>
       </c>
       <c r="H64" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K64" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L64" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M64">
         <v>1.1101171637805711</v>
       </c>
-      <c r="N64" s="4" t="s">
-        <v>33</v>
+      <c r="N64" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O64" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q64" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U64" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X64" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z64" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B65">
         <v>3</v>
       </c>
       <c r="C65" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D65">
         <v>14</v>
       </c>
       <c r="E65" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F65">
         <v>1405</v>
       </c>
       <c r="H65" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K65" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L65" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M65">
         <v>0.78463745478411639</v>
       </c>
-      <c r="N65" s="5" t="s">
-        <v>36</v>
+      <c r="N65" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="O65" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q65" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="T65" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U65" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X65" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z65" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B66">
         <v>3</v>
       </c>
       <c r="C66" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D66">
         <v>14</v>
       </c>
       <c r="E66" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F66">
         <v>1406</v>
       </c>
       <c r="H66" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K66" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L66" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M66">
         <v>0.74476679127485423</v>
       </c>
-      <c r="N66" s="6" t="s">
-        <v>38</v>
+      <c r="N66" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="O66" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q66" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U66" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z66" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B67">
         <v>3</v>
       </c>
       <c r="C67" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D67">
         <v>15</v>
       </c>
       <c r="E67" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F67">
         <v>1501</v>
       </c>
       <c r="H67" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K67" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L67" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M67">
         <v>0.92675618848689845</v>
       </c>
-      <c r="N67" s="5" t="s">
-        <v>36</v>
+      <c r="N67" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="O67" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q67" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="T67" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U67" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X67" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z67" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B68">
         <v>3</v>
       </c>
       <c r="C68" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D68">
         <v>15</v>
       </c>
       <c r="E68" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="F68">
         <v>1502</v>
       </c>
       <c r="H68" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I68" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K68" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L68" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M68">
         <v>0.74528528339746158</v>
       </c>
-      <c r="N68" s="5" t="s">
-        <v>36</v>
+      <c r="N68" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="O68" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q68" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="T68" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U68" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="V68" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X68" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z68" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B69">
         <v>3</v>
       </c>
       <c r="C69" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D69">
         <v>15</v>
       </c>
       <c r="E69" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="F69">
         <v>1503</v>
       </c>
       <c r="H69" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I69" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K69" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L69" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M69">
         <v>0.62641485647777995</v>
       </c>
-      <c r="N69" s="4" t="s">
-        <v>33</v>
+      <c r="N69" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O69" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q69" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U69" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="V69" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X69" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z69" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B70">
         <v>3</v>
       </c>
       <c r="C70" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D70">
         <v>15</v>
       </c>
       <c r="E70" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F70">
         <v>1504</v>
       </c>
       <c r="H70" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K70" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L70" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M70">
         <v>0.88489011639261184</v>
       </c>
-      <c r="N70" s="5" t="s">
-        <v>36</v>
+      <c r="N70" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="O70" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q70" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="T70" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U70" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X70" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z70" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B71">
         <v>4</v>
       </c>
       <c r="C71" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D71">
         <v>16</v>
       </c>
       <c r="E71" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F71">
         <v>1601</v>
       </c>
       <c r="J71" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K71" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L71" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M71">
         <v>0.81647723554446305</v>
       </c>
-      <c r="N71" s="4" t="s">
-        <v>33</v>
+      <c r="N71" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O71" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q71" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S71" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U71" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X71" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z71" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B72">
         <v>4</v>
       </c>
       <c r="C72" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D72">
         <v>17</v>
       </c>
       <c r="E72" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="F72">
         <v>1701</v>
       </c>
       <c r="H72" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J72" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K72" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L72" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M72">
         <v>1.3642964367701933</v>
       </c>
-      <c r="N72" s="5" t="s">
-        <v>36</v>
+      <c r="N72" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="O72" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q72" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S72" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="T72" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U72" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X72" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z72" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AA72" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B73">
         <v>4</v>
       </c>
       <c r="C73" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D73">
         <v>17</v>
       </c>
       <c r="E73" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F73">
         <v>1702</v>
       </c>
       <c r="H73" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J73" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K73" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L73" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M73">
         <v>1.8194283004256537</v>
       </c>
-      <c r="N73" s="5" t="s">
-        <v>36</v>
+      <c r="N73" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="O73" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q73" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S73" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="T73" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U73" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X73" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z73" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AA73" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="74" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B74">
         <v>4</v>
       </c>
       <c r="C74" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D74">
         <v>18</v>
       </c>
       <c r="E74" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="F74">
         <v>1801</v>
       </c>
       <c r="H74" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J74" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K74" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L74" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M74">
         <v>1.8872393623135464</v>
       </c>
-      <c r="N74" s="4" t="s">
-        <v>33</v>
+      <c r="N74" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O74" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q74" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S74" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U74" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X74" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z74" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="75" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B75">
         <v>4</v>
       </c>
       <c r="C75" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D75">
         <v>18</v>
       </c>
       <c r="E75" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="F75">
         <v>1802</v>
       </c>
       <c r="H75" t="s">
-        <v>29</v>
-      </c>
-      <c r="I75" s="9"/>
+        <v>23</v>
+      </c>
       <c r="J75" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K75" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L75" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M75">
         <v>1.2817676403924969</v>
       </c>
-      <c r="N75" s="4" t="s">
-        <v>33</v>
+      <c r="N75" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O75" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q75" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S75" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U75" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X75" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z75" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B76">
         <v>4</v>
       </c>
       <c r="C76" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D76">
         <v>18</v>
       </c>
       <c r="E76" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F76">
         <v>1803</v>
       </c>
       <c r="H76" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J76" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K76" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L76" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M76">
         <v>1.0483673981855122</v>
       </c>
-      <c r="N76" s="5" t="s">
-        <v>36</v>
+      <c r="N76" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="O76" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q76" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S76" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="T76" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U76" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X76" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z76" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AA76" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="77" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B77">
         <v>4</v>
       </c>
       <c r="C77" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D77">
         <v>18</v>
       </c>
       <c r="E77" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="F77">
         <v>1804</v>
       </c>
       <c r="H77" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J77" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K77" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L77" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M77">
         <v>0.57480993808581748</v>
       </c>
-      <c r="N77" s="5" t="s">
-        <v>36</v>
+      <c r="N77" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="O77" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q77" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S77" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="T77" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U77" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X77" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z77" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AA77" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A78" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="B78" s="9">
+      <c r="A78" t="s">
+        <v>125</v>
+      </c>
+      <c r="B78">
         <v>4</v>
       </c>
-      <c r="C78" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="D78" s="9">
+      <c r="C78" t="s">
+        <v>136</v>
+      </c>
+      <c r="D78">
         <v>19</v>
       </c>
-      <c r="E78" s="9" t="s">
-        <v>143</v>
+      <c r="E78" t="s">
+        <v>137</v>
       </c>
       <c r="F78">
         <v>1901</v>
       </c>
       <c r="I78" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K78" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L78" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M78">
         <v>1.0423607885134925</v>
       </c>
-      <c r="N78" s="5" t="s">
-        <v>36</v>
+      <c r="N78" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="O78" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q78" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U78" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="V78" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X78" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z78" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="79" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A79" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="B79" s="9">
+      <c r="A79" t="s">
+        <v>125</v>
+      </c>
+      <c r="B79">
         <v>4</v>
       </c>
-      <c r="C79" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="D79" s="9">
+      <c r="C79" t="s">
+        <v>136</v>
+      </c>
+      <c r="D79">
         <v>19</v>
       </c>
-      <c r="E79" s="9" t="s">
-        <v>144</v>
+      <c r="E79" t="s">
+        <v>138</v>
       </c>
       <c r="F79">
         <v>1902</v>
       </c>
       <c r="K79" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L79" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M79">
         <v>2.6667677567733792</v>
       </c>
-      <c r="N79" s="4" t="s">
-        <v>33</v>
+      <c r="N79" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O79" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q79" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U79" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="X79" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z79" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A80" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="B80" s="9">
+      <c r="A80" t="s">
+        <v>125</v>
+      </c>
+      <c r="B80">
         <v>4</v>
       </c>
-      <c r="C80" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="D80" s="9">
+      <c r="C80" t="s">
+        <v>139</v>
+      </c>
+      <c r="D80">
         <v>20</v>
       </c>
-      <c r="E80" s="9" t="s">
-        <v>146</v>
+      <c r="E80" t="s">
+        <v>140</v>
       </c>
       <c r="F80">
         <v>2001</v>
       </c>
       <c r="H80" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J80" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K80" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L80" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M80">
         <v>0.81269972113566813</v>
       </c>
-      <c r="N80" s="6" t="s">
-        <v>38</v>
+      <c r="N80" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="O80" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q80" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U80" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z80" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="81" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A81" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="B81" s="9">
+      <c r="A81" t="s">
+        <v>125</v>
+      </c>
+      <c r="B81">
         <v>4</v>
       </c>
-      <c r="C81" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="D81" s="9">
+      <c r="C81" t="s">
+        <v>139</v>
+      </c>
+      <c r="D81">
         <v>20</v>
       </c>
-      <c r="E81" s="9" t="s">
-        <v>147</v>
+      <c r="E81" t="s">
+        <v>141</v>
       </c>
       <c r="F81">
         <v>2002</v>
       </c>
       <c r="H81" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J81" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K81" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L81" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M81">
         <v>1.5104493981823033</v>
       </c>
-      <c r="N81" s="6" t="s">
-        <v>38</v>
+      <c r="N81" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="O81" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q81" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U81" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z81" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="82" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A82" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="B82" s="9">
+      <c r="A82" t="s">
+        <v>125</v>
+      </c>
+      <c r="B82">
         <v>4</v>
       </c>
-      <c r="C82" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="D82" s="9">
+      <c r="C82" t="s">
+        <v>139</v>
+      </c>
+      <c r="D82">
         <v>20</v>
       </c>
-      <c r="E82" s="9" t="s">
-        <v>148</v>
+      <c r="E82" t="s">
+        <v>142</v>
       </c>
       <c r="F82">
         <v>2003</v>
       </c>
       <c r="G82" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H82" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J82" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K82" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L82" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M82">
         <v>1.1315589792662066</v>
       </c>
-      <c r="N82" s="8" t="s">
-        <v>77</v>
+      <c r="N82" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="O82" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R82" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U82" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W82" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y82" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z82" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A83" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B83" s="9">
+      <c r="A83" t="s">
+        <v>55</v>
+      </c>
+      <c r="B83">
         <v>2</v>
       </c>
-      <c r="C83" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="D83" s="9">
+      <c r="C83" t="s">
+        <v>143</v>
+      </c>
+      <c r="D83">
         <v>21</v>
       </c>
-      <c r="E83" s="9" t="s">
-        <v>150</v>
+      <c r="E83" t="s">
+        <v>144</v>
       </c>
       <c r="F83">
         <v>2104</v>
       </c>
       <c r="J83" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K83" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="M83">
         <v>1.2483079881665222</v>
       </c>
-      <c r="N83" s="6" t="s">
-        <v>38</v>
+      <c r="N83" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P83" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q83" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U83" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z83" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="84" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A84" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B84" s="9">
+      <c r="A84" t="s">
+        <v>55</v>
+      </c>
+      <c r="B84">
         <v>2</v>
       </c>
-      <c r="C84" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="D84" s="9">
+      <c r="C84" t="s">
+        <v>143</v>
+      </c>
+      <c r="D84">
         <v>21</v>
       </c>
-      <c r="E84" s="9" t="s">
-        <v>151</v>
+      <c r="E84" t="s">
+        <v>145</v>
       </c>
       <c r="F84">
         <v>2105</v>
       </c>
       <c r="J84" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K84" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="M84">
         <v>0.9588238168963894</v>
       </c>
-      <c r="N84" s="6" t="s">
-        <v>38</v>
+      <c r="N84" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P84" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q84" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U84" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z84" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="85" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A85" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B85" s="9">
+      <c r="A85" t="s">
+        <v>55</v>
+      </c>
+      <c r="B85">
         <v>2</v>
       </c>
-      <c r="C85" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="D85" s="9">
+      <c r="C85" t="s">
+        <v>143</v>
+      </c>
+      <c r="D85">
         <v>21</v>
       </c>
-      <c r="E85" s="9" t="s">
-        <v>152</v>
+      <c r="E85" t="s">
+        <v>146</v>
       </c>
       <c r="F85">
         <v>2108</v>
       </c>
       <c r="J85" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K85" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="M85">
         <v>1.0313441586631378</v>
       </c>
-      <c r="N85" s="6" t="s">
-        <v>38</v>
+      <c r="N85" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="P85" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q85" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U85" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z85" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="86" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A86" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B86" s="9">
+      <c r="A86" t="s">
+        <v>55</v>
+      </c>
+      <c r="B86">
         <v>2</v>
       </c>
-      <c r="C86" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="D86" s="9">
+      <c r="C86" t="s">
+        <v>147</v>
+      </c>
+      <c r="D86">
         <v>22</v>
       </c>
-      <c r="E86" s="9" t="s">
-        <v>154</v>
+      <c r="E86" t="s">
+        <v>148</v>
       </c>
       <c r="F86">
         <v>2201</v>
       </c>
       <c r="G86" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="J86" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K86" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L86" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M86">
         <v>1.4857716069492239</v>
       </c>
-      <c r="N86" s="8" t="s">
-        <v>77</v>
+      <c r="N86" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="O86" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R86" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U86" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W86" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y86" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z86" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="87" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A87" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B87" s="9">
+      <c r="A87" t="s">
+        <v>55</v>
+      </c>
+      <c r="B87">
         <v>2</v>
       </c>
-      <c r="C87" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="D87" s="9">
+      <c r="C87" t="s">
+        <v>147</v>
+      </c>
+      <c r="D87">
         <v>22</v>
       </c>
-      <c r="E87" s="9" t="s">
-        <v>155</v>
+      <c r="E87" t="s">
+        <v>149</v>
       </c>
       <c r="F87">
         <v>2204</v>
       </c>
       <c r="G87" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="I87" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J87" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K87" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L87" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M87">
         <v>3.673953054858111</v>
       </c>
-      <c r="N87" s="8" t="s">
-        <v>77</v>
+      <c r="N87" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="O87" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R87" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U87" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W87" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y87" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z87" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="88" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A88" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B88" s="9">
+      <c r="A88" t="s">
+        <v>55</v>
+      </c>
+      <c r="B88">
         <v>2</v>
       </c>
-      <c r="C88" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="D88" s="9">
+      <c r="C88" t="s">
+        <v>147</v>
+      </c>
+      <c r="D88">
         <v>22</v>
       </c>
-      <c r="E88" s="9" t="s">
-        <v>156</v>
+      <c r="E88" t="s">
+        <v>150</v>
       </c>
       <c r="F88">
         <v>2206</v>
       </c>
       <c r="G88" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="J88" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K88" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="M88">
         <v>1.3510094591323287</v>
       </c>
-      <c r="N88" s="8" t="s">
-        <v>77</v>
+      <c r="N88" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="P88" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R88" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="U88" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="W88" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y88" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z88" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
